--- a/www/download/COUNTRY.IND.rpPE.xlsx
+++ b/www/download/COUNTRY.IND.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Índia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>32.3624597460212</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>35.4233080157224</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>36.2844710313904</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>41.203131834449</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>43.0477838422277</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>44.9034582986076</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>47.1920697216164</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>48.6144866907991</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>46.554935412596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>45.3103761812977</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>44.0917118830387</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>45.2898541499635</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>41.2711521319086</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>43.2393174685843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>48.3687622444747</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>380.787</t>
+          <t>20.3948316737812</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>393.501</t>
+          <t>22.3030882333846</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>397.971</t>
+          <t>19.1783641156966</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>401.547</t>
+          <t>18.7678308482706</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>398.413</t>
+          <t>18.5657869990881</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>416.883</t>
+          <t>18.4566396940521</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>432.376</t>
+          <t>18.1710066015523</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>424.206</t>
+          <t>18.0726069388366</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>449.023</t>
+          <t>16.9536607505105</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>457.9</t>
+          <t>16.5179838675117</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>469.777</t>
+          <t>15.0719724831231</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>471.768</t>
+          <t>14.1439002339567</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>460.23</t>
+          <t>12.6941039334759</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>463.379</t>
+          <t>12.7481125790165</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>465.828</t>
+          <t>11.8811044711881</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>176.495</t>
+          <t>20.2438923612837</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>182.775</t>
+          <t>21.8427168752073</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>185.732</t>
+          <t>18.5913333009883</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>188.117</t>
+          <t>18.3940101195138</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>187.86</t>
+          <t>18.3249391839409</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>194.375</t>
+          <t>18.9773125969665</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>198.162</t>
+          <t>19.1817425747124</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>192.288</t>
+          <t>19.2066798120969</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>198.163</t>
+          <t>18.6042892292099</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>198.994</t>
+          <t>18.2951488190166</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>199.767</t>
+          <t>16.6120432392629</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>197.538</t>
+          <t>15.3033635121942</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>191.106</t>
+          <t>13.4140327827262</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>193.616</t>
+          <t>13.5119740846294</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>195.621</t>
+          <t>12.3214236708917</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>883269.411</t>
+          <t>15.2635925208634</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>912034.175</t>
+          <t>16.7669745424239</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>921899.495</t>
+          <t>14.3163765485035</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>929558.011</t>
+          <t>14.1136811745894</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>921995.643</t>
+          <t>13.8495191562088</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>963502.007</t>
+          <t>13.8369723791934</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1001482.189</t>
+          <t>13.4001914544419</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>985730.519</t>
+          <t>12.9410006257618</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1045978.848</t>
+          <t>13.4199352835383</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1068687.044</t>
+          <t>11.9271572521443</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1098153.176</t>
+          <t>10.8289735541855</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1102781.829</t>
+          <t>10.2971071380366</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1077429.619</t>
+          <t>9.30495928368333</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1085691.063</t>
+          <t>9.76936242539454</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1092178.443</t>
+          <t>8.79503596799979</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>408729.533</t>
+          <t>2241634268951.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>422740.685</t>
+          <t>2275860098527.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>429173.719</t>
+          <t>2357707616321.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>434229.587</t>
+          <t>2448896597687.93</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>433336.133</t>
+          <t>2463220456616.64</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>447690.05</t>
+          <t>2680537496308.65</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>457931.785</t>
+          <t>2835940099196.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>446355.698</t>
+          <t>2810390107769.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>461695.026</t>
+          <t>2850203932774.58</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>465360.993</t>
+          <t>3067756900026.48</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>468780.92</t>
+          <t>3072739597809.27</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>463833.094</t>
+          <t>3039577466987.46</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>449591.928</t>
+          <t>2861642025806.65</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>455869.88</t>
+          <t>2758825654473.71</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>460912.884</t>
+          <t>2842416931060.79</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>42537477147.0731</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>40318135260.9091</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>48115209093.0485</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>51223384435.6255</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>53031623197.2766</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>56409313574.785</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>59659315348.1878</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>60066604250.62</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>60314922756.6474</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>67128328496.0511</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>72709534354.5374</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>75096750504.1823</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>78182766967.1801</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>75713883017.91</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>83935700624.7757</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>68489093.5025377</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>66714591.2645415</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>63059202.5048447</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>65406963.361143</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>64899296.1630036</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>69636048.3846924</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>75152484.779004</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>73692358.1846459</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>63582241.0243039</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>59814364.784713</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>50983891.8097905</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>43826895.3712811</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>32999788.5005652</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>30156769.3186479</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>30686145.2219444</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>4427738.02637397</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>4622292.20393484</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>4638312.5586997</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>4625868.70887287</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>4756987.03288277</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>5076831.78832807</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>5207010.09929194</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>5330394.98524708</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>6170329.97738708</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>6929329.37823123</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>7594883.47694969</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>7984495.8226159</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>8827054.88993747</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>9764830.98727841</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>9064805.92709822</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>7396104.46313576</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>7596105.0216686</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>7699055.25389793</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>7586880.91231301</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>7725773.14704453</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>8179473.00702757</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>8347547.81273303</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>8493235.82858681</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>9986249.66225684</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>11165671.661365</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>12117711.271609</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>12746200.5795377</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>14184342.2058904</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>15537673.4473596</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>14746445.1338215</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>18.3269982077914</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>19.9749632646574</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.18</t>
+          <t>17.1050805040679</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>48.83</t>
+          <t>16.9355438664786</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>16.8180018856503</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>48.41</t>
+          <t>17.1153614560686</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>47.29</t>
+          <t>16.9944220481114</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>16.8494205637114</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>16.439302858394</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>15.6941971335656</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>14.2482938242626</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>13.3131402257566</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>11.8450167714403</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>12.0496532338237</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>11.0327355929428</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>79659.7714734204</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>81953.3621818118</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>83116.05102857</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>79258.8713993947</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>86424.6759602973</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>91264.8480153773</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>97869.6705282442</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>102907.829816439</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>120416.277661068</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>138799.355526106</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>166184.524876129</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>191436.933187129</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>19.52</t>
+          <t>247279.834367286</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>20.12</t>
+          <t>268488.565290632</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>276598.975512559</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>32.3624597460212</t>
+          <t>241.012689081977</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35.4233080157224</t>
+          <t>220.589463262694</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36.2844710313904</t>
+          <t>259.057288444936</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.203131834449</t>
+          <t>272.29509448417</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>43.0477838422277</t>
+          <t>282.292895418833</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.9034582986076</t>
+          <t>290.208487441464</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>47.1920697216164</t>
+          <t>301.063759810143</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48.6144866907991</t>
+          <t>312.377710696452</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>46.554935412596</t>
+          <t>304.370115862061</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>45.3103761812977</t>
+          <t>337.338428707772</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>44.0917118830387</t>
+          <t>363.972110355627</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>45.2898541499635</t>
+          <t>380.163005248886</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>41.2711521319086</t>
+          <t>409.107763687512</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>43.2393174685843</t>
+          <t>391.052391917342</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>48.3687622444747</t>
+          <t>429.07303095302</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>-106803295920.86</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-110648265901.284</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-119344489641.316</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-123156157296.048</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>-132649472526.073</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>-163588531245.644</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>-163262668217.664</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>-167890837248.786</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>-144149308812.116</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-162339797697.36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>-152853670949.477</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>-166829948082.885</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>-147829324105.35</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>-144352691945.987</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>-104485524913.869</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>-106208940488.852</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>-110666193999.452</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>-119382294184.667</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>-123260429537.791</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>-133410434491.904</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>-165379529004.394</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>-165952421090.723</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>-172294519060.563</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-150442991927.003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>-171260907712.493</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>-162882131755.342</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>-176935295395.455</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>-157908215206.014</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>-153720934290.131</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>-111715050053.67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>-594355432.008232</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>17928098.168366</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>37804543.3507413</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>104272241.742359</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>760961965.83127</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1790997758.7506</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>2689752873.05931</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>4403681811.77662</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>6293683114.88666</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>8921110015.13306</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>10028460805.8646</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>10105347312.5697</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>10078891100.6637</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>9368242344.14443</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>7229525139.80153</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>4658.05180994234</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>4626.8558885055</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>4690.25306246111</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>4883.76061174777</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>5029.89534287845</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>5257.23164762105</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>5417.46835741496</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>5575.76113295034</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>5308.00263156295</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>5631.59422957483</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>5549.95368253954</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>5441.32640277234</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.341</t>
+          <t>5254.99608589251</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.544</t>
+          <t>5103.09811077862</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>5162.92233152024</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>4833.23449161165</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>4804.15070127162</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>4886.16675541791</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>5122.79345621415</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>5289.02293514886</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>5531.98140373762</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>5661.27967936789</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>5777.22797384733</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>5476.02962034879</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>5794.8308100254</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>5675.62157112688</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>5555.91029537603</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>5347.29179801301</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>5175.23386020845</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>5214.36031838014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2039.48</t>
+          <t>42190.4443609062</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2230.31</t>
+          <t>44308.7304213983</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1917.84</t>
+          <t>47568.3231940199</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1876.78</t>
+          <t>49617.2512347252</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1856.58</t>
+          <t>55007.2540389052</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1845.66</t>
+          <t>67708.288287402</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1817.1</t>
+          <t>66875.4175146345</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1807.26</t>
+          <t>77841.1161473401</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1695.37</t>
+          <t>88181.7103564999</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1651.8</t>
+          <t>123820.217757189</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1507.2</t>
+          <t>157727.971292324</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1414.39</t>
+          <t>198123.928664349</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1269.41</t>
+          <t>242725.113223604</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1274.81</t>
+          <t>259622.878233011</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1188.11</t>
+          <t>227253.968468943</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024.39</t>
+          <t>128426521039.33</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2184.27</t>
+          <t>132139088675.038</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1859.13</t>
+          <t>141678322001.711</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1839.4</t>
+          <t>151014586084.482</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1832.49</t>
+          <t>170774528321.412</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1897.73</t>
+          <t>208377006683.998</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1918.17</t>
+          <t>210849250322.425</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1920.67</t>
+          <t>219904995850.271</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1860.43</t>
+          <t>196527171416.163</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1829.51</t>
+          <t>239710554346.161</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1661.2</t>
+          <t>244732368216.886</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1530.34</t>
+          <t>251182383107.677</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1341.4</t>
+          <t>236257521346.964</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1351.2</t>
+          <t>230772678619.332</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1232.14</t>
+          <t>200092547178.094</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1526.36</t>
+          <t>43742.1386943222</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1676.7</t>
+          <t>45931.4174722332</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1431.64</t>
+          <t>49032.7622933105</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1411.37</t>
+          <t>52971.8074865367</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1384.95</t>
+          <t>59759.2850203407</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1383.7</t>
+          <t>66742.1545757755</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1340.02</t>
+          <t>65686.0833914531</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1294.1</t>
+          <t>74883.5861957074</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1341.99</t>
+          <t>86656.9215268048</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1192.72</t>
+          <t>128122.543510154</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1082.9</t>
+          <t>169922.116329699</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1029.71</t>
+          <t>213375.178266109</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>930.5</t>
+          <t>268350.444200915</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>976.94</t>
+          <t>294846.686007943</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>879.5</t>
+          <t>267974.340420028</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1840434.938</t>
+          <t>22221415445.2972</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1890437.327</t>
+          <t>22094901832.8063</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1944551.481</t>
+          <t>22843071618.7585</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2057041.707</t>
+          <t>29154305528.7082</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2107214.58</t>
+          <t>40072561879.7177</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2306190.438</t>
+          <t>44370034991.1452</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2447800.054</t>
+          <t>47041319783.235</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2450733.572</t>
+          <t>50680221520.4115</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2458864.621</t>
+          <t>51778997290.8423</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2653450.849</t>
+          <t>79007196077.8174</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2666277.786</t>
+          <t>96113612455.7386</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2621100.453</t>
+          <t>89112763979.5703</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2460984.537</t>
+          <t>95146408589.8904</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2398092.978</t>
+          <t>94446050577.2006</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2428993.344</t>
+          <t>105994996033.059</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>822121.745</t>
+          <t>-1551.69433341598</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>845671.406</t>
+          <t>-1622.68705083492</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>871129.734</t>
+          <t>-1464.43909929061</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>918719.259</t>
+          <t>-3354.55625181147</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>944917.562</t>
+          <t>-4752.03098143559</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1021875.105</t>
+          <t>966.133711626524</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1073534.899</t>
+          <t>1189.33412318138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1072154.081</t>
+          <t>2957.52995163274</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1051850.205</t>
+          <t>1524.78882969508</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1120653.549</t>
+          <t>-4302.32575296547</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1108696.344</t>
+          <t>-12194.145037375</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1074870.32</t>
+          <t>-15251.2496017601</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1004258.953</t>
+          <t>-25625.3309773102</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>988039.918</t>
+          <t>-35223.8077749327</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1009976.092</t>
+          <t>-40720.3719510847</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2241634.269</t>
+          <t>106205105594.033</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2275860.099</t>
+          <t>110044186842.232</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2357707.616</t>
+          <t>118835250382.952</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2448896.598</t>
+          <t>121860280555.774</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2463220.457</t>
+          <t>130701966441.694</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2680537.496</t>
+          <t>164006971692.853</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2835940.099</t>
+          <t>163807930539.19</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2810390.108</t>
+          <t>169224774329.859</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2850203.933</t>
+          <t>144748174125.321</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3067756.9</t>
+          <t>160703358268.344</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3072739.598</t>
+          <t>148618755761.147</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3039577.467</t>
+          <t>162069619128.107</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2861642.026</t>
+          <t>141111112757.074</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2758825.654</t>
+          <t>136326628042.131</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2842416.931</t>
+          <t>94097551145.0348</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7.396</t>
+          <t>223060.94208</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7.596</t>
+          <t>238101.96924</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7.699</t>
+          <t>254778.66558</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7.587</t>
+          <t>256143.10173</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>7.726</t>
+          <t>266821.27946</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8.179</t>
+          <t>271913.7645</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>8.348</t>
+          <t>275570.49268</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>8.493</t>
+          <t>284632.24895</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>9.986</t>
+          <t>334641.38392</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>11.166</t>
+          <t>391168.90014</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>12.118</t>
+          <t>461093.23389</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>12.746</t>
+          <t>519295.997</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>14.184</t>
+          <t>653130.30221</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>15.538</t>
+          <t>701350.80033</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>14.746</t>
+          <t>712642.83225</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1341972.567</t>
+          <t>0.0853601014596236</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1384879.535</t>
+          <t>0.106629137080085</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1420406.074</t>
+          <t>0.105335874398919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1493139.839</t>
+          <t>0.120755109345244</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1516677.69</t>
+          <t>0.125374515917872</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1663754.86</t>
+          <t>0.117513751566945</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1768994.808</t>
+          <t>0.10902738797338</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1763814.127</t>
+          <t>0.108536406939624</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1761091.437</t>
+          <t>0.112044799891841</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1903826.179</t>
+          <t>0.112192952735706</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1925866.913</t>
+          <t>0.114306947854305</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1904057.09</t>
+          <t>0.113735137375341</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1780827.822</t>
+          <t>0.112666402508448</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1733815.962</t>
+          <t>0.114776018866656</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1747265.704</t>
+          <t>0.116294885052</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4.428</t>
+          <t>123613.527569007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.622</t>
+          <t>120048.866053424</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4.638</t>
+          <t>139339.845934098</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4.626</t>
+          <t>139753.09091733</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4.757</t>
+          <t>146077.221231</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5.077</t>
+          <t>148492.076719936</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5.207</t>
+          <t>152614.816485931</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>157697.743396309</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>182469.015584059</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6.929</t>
+          <t>210392.821080105</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>7.595</t>
+          <t>245138.93048999</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7.984</t>
+          <t>272797.882795781</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>8.827</t>
+          <t>337414.481954298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>9.765</t>
+          <t>368490.321395703</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>9.065</t>
+          <t>386510.154509205</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>42537.477</t>
+          <t>198089.070790303</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>40318.135</t>
+          <t>196162.657726759</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48115.209</t>
+          <t>221371.657877838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>51223.384</t>
+          <t>219220.329306488</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>53031.623</t>
+          <t>228724.289692498</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>56409.314</t>
+          <t>236706.271197512</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>59659.315</t>
+          <t>247082.297465197</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>60066.604</t>
+          <t>257128.621463448</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>60314.923</t>
+          <t>299841.647733577</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>67128.328</t>
+          <t>347623.532582441</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>72709.534</t>
+          <t>404651.235885026</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>75096.751</t>
+          <t>454079.252238379</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>78182.767</t>
+          <t>567246.968696692</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>75713.883</t>
+          <t>617745.031017299</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>83935.701</t>
+          <t>643862.68391602</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1832.7</t>
+          <t>843277.635398844</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1997.5</t>
+          <t>876969.433422282</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1710.51</t>
+          <t>942357.87911787</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1693.55</t>
+          <t>916608.381659981</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1681.8</t>
+          <t>958236.780478598</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1711.54</t>
+          <t>1022074.4888626</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1699.44</t>
+          <t>1089764.88600799</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1684.94</t>
+          <t>1159366.17728751</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1643.93</t>
+          <t>1337197.4616402</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1569.42</t>
+          <t>1579909.15284148</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1424.83</t>
+          <t>1842048.50694835</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1331.31</t>
+          <t>2075769.18525513</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1184.5</t>
+          <t>2658636.57804784</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1204.97</t>
+          <t>2948367.05553636</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1103.27</t>
+          <t>2990188.09248265</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>68.489</t>
+          <t>198089.070790303</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>66.715</t>
+          <t>198694.967531973</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>63.059</t>
+          <t>214749.468349746</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>65.407</t>
+          <t>222901.514059908</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>64.899</t>
+          <t>234115.619268022</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>69.636</t>
+          <t>246559.834273214</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>75.152</t>
+          <t>263107.175047203</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>73.692</t>
+          <t>273303.033492786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>63.582</t>
+          <t>293967.325335853</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>59.814</t>
+          <t>314411.843292728</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>50.984</t>
+          <t>342574.500922912</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>43.827</t>
+          <t>377898.744723867</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>410522.763912039</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>30.157</t>
+          <t>438591.361179476</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>30.686</t>
+          <t>482183.000180849</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>123613.527569007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>121832.953115175</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>135504.481687451</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>141712.786034959</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>148679.592805464</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>153851.37034201</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>160976.186305388</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>166410.482191631</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>177484.835356938</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>188824.925215769</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>207129.94008064</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>228277.309557297</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>246120.937408318</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>263931.76050548</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>293786.840308781</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>151642.035989697</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>175463.856113241</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>182380.142222162</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>189944.016753512</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>206563.148447502</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>211372.655582488</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>216683.889554803</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>228741.269026552</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>270242.299666423</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>316054.028437559</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>376743.467504974</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>427524.826631621</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>546818.853193308</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>606890.398082701</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>624342.556011689</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>822121744585.448</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>845671405997.054</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>871129734099.705</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>918719258534.658</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>944917562128.169</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1021875104895.95</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1073534899476.66</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1072154081103.33</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1051850204833.81</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1120653549159.83</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1108696343663.3</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1074870320465.02</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1004258952931.03</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>988039918370.015</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1009976092426.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1840434937820.31</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1890437327176.16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1944551480574.38</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2057041707282.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2107214579660.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2306190437574.09</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2447800053530.15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2450733572443.73</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2458864621318.49</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2653450849054.25</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2666277786429.42</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2621100452690.32</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2460984537330.17</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2398092978282.19</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2428993344008.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1341972567225.11</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1384879535059.03</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1420406073977.77</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1493139838813.7</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1516677690146.71</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1663754860413.74</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1768994807670.4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1763814126839.49</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1761091437012.11</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1903826178785.05</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1925866913090.1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1904057090286.2</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1780827822009.07</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1733815962252.8</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1747265704387.91</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>380787429.414916</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>393500838.072331</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>397970756.609609</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>401546875.716261</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>398412827</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>416883259.227144</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>432375751.095812</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>424205792.732751</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>449023250.747477</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>457899624</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>469777231.09542</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>471767957.605752</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>460230081</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>463378669.072472</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>465827675.054621</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>176494761.786607</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>182774529.04854</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>185731925.86811</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>188117176.817533</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>187860282.911458</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>194375133.794676</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>198161729.547954</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>192288381.001002</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>198163090.308057</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>198994015.455626</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>199766774.117651</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>197538291.383765</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>191105556.791384</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>193615701.074433</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>195621012.204717</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>883269411041.813</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>912034175416.31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>921899495067.775</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>929558010777.49</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>921995642624.479</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>963502007286.061</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1001482188929.38</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>985730519159.591</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1045978847742.94</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1068687043754.34</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1098153176017.84</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1102781829254.43</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1077429618585.69</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1085691063414.01</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1092178442629.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>408729532907.89</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>422740684945.954</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>429173719058.416</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>434229587334.143</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>433336132594.373</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>447690050382.461</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>457931785421.459</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>446355698248.271</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>461695025670.482</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>465360993412.491</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>468780919950.533</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>463833093857.914</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>449591927559.544</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>455869880085.226</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>460912884317.789</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.215449898684455</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.215273192986451</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.215096487288446</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.214919781590441</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.214743075892436</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.235313607787725</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.255884139683014</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.276454671578303</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.297025203473592</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.426572864616802</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.434971395509284</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.443369926401766</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.451768457294249</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.460166988186731</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.444450156426241</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.428733324665752</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.413016492905263</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.397299661144773</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.357977236698742</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.349755411504265</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.341533586309788</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.333311761115311</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.325089935920834</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.320236235786034</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.315382535651234</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.310528835516434</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.305675135381635</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.287574730278196</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.291818090657168</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.295885776350188</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.302730361537393</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.305783499312606</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.326498463449756</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.34280659440456</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.358516762729589</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.369000710077315</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.384828271046484</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.38303912572535</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.381584818554321</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.376145206335676</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.372770946799532</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.375709448938946</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.477421320575452</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.478000622806635</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.481753853650408</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.488299635922274</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.495083337002571</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.484107127101319</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.472888001785081</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.459951296123359</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.440913241052009</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.435599540970021</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.434450759157723</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.431876180798955</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.428698014983939</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.426071909389533</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.424337408586454</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.235003949146351</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.230181286536197</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.222360369999404</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.208970002540333</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.199133163684823</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.189394409448924</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.184305403810359</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.181531941147052</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.190086048870676</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.179572187983495</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.182510115116927</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.186539000646723</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.195156778680385</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.201157143810935</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.199953142474599</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>727386.69902</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>754103.19355</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>829047.77571</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>827157.17116</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>866029.74744</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>902411.61575</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>925415.9909</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>982647.65615</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1159060.31364</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1371614.28394</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1610529.88414</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1853051.59181</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2340827.68566</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2543922.83553</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2590618.46841</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>349731.10678</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>371626.51384</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>403751.8001</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>409164.34606</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>435287.43814</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>448078.92678</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>463766.18702</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>485869.89049</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>570083.9474</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>663677.56102</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>781394.70339</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>881604.07887</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1114065.82189</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1224635.4291</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1257941.60896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27290538.2703555</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28899654.6865236</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>30607050.1499728</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>32478160.0391071</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>34677209.4583278</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>36797855.1862464</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>38953160.9736572</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>41336712.5276652</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>44143087.0870978</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>47903642.9233841</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>52426737.6630606</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>57618923.0172985</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>63852466.1292683</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>69625755.9629028</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>75835204.2729793</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
